--- a/docs/master/pegawai.xlsx
+++ b/docs/master/pegawai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\penatausahaan\docs\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D3D63B-F6C0-4B64-BCA0-DC2E024A44B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4060121-E9F3-49AE-8493-DE23063FBA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C4C0E749-8BBB-49E9-ADA1-A5E766212CC7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="372">
   <si>
     <t/>
   </si>
@@ -1134,6 +1134,119 @@
   </si>
   <si>
     <t>198409202024212002</t>
+  </si>
+  <si>
+    <t>5.1.01.01.009.00001 BPJS Kesehatan Gaji (1%)Rp 80.900</t>
+  </si>
+  <si>
+    <t>5.1.01.01.013.00001 Taspen — Iuran Pensiun (4,75%)Rp 288.086</t>
+  </si>
+  <si>
+    <t>5.1.01.01.013.00001 Taspen — JHT (3,25%)Rp 197.111</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5.1.01.01.007.00001 Tunjangan PPh 21 — Ditanggung Pemerintah </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(disetor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rp 123.522</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5.1.01.01.009.00001 BPJS Kesehatan — Pemberi Kerja (4%) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(disetor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rp 323.598</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5.1.01.01.010.00001 Iuran JKK — Pemberi Kerja (0,24%) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(disetor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rp 13.233</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5.1.01.01.011.00001 Iuran JKM — Pemberi Kerja (0,30%) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(disetor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rp 39.698</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1143,7 +1256,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1156,6 +1269,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1197,7 +1318,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
@@ -1206,6 +1327,9 @@
     <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1522,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816F0895-CD4F-4DBB-9AC3-12375A5F2538}">
-  <dimension ref="A1:CW28"/>
+  <dimension ref="A1:CW38"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2452,305 +2576,305 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:101" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+    <row r="4" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
         <v>46204</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="D4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="8">
         <v>25876</v>
       </c>
-      <c r="I4" s="4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="9">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="8">
         <v>33664</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="8">
         <v>33664</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="9">
         <v>29</v>
       </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
         <v>46082</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="8">
         <v>46447</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="Q4" s="9">
         <v>58</v>
       </c>
-      <c r="R4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="s">
+      <c r="R4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AB4" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AC4" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AD4" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AE4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AF4" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="AG4" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="3">
+      <c r="AG4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="8">
         <v>46204</v>
       </c>
-      <c r="AI4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="4">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="4">
+      <c r="AI4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="9">
         <v>4</v>
       </c>
-      <c r="AO4" s="4" t="s">
+      <c r="AO4" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AP4" s="9">
         <v>29</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AQ4" s="9">
         <v>100</v>
       </c>
-      <c r="AR4" s="3">
+      <c r="AR4" s="8">
         <v>45292</v>
       </c>
-      <c r="AS4" s="4" t="s">
+      <c r="AS4" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AT4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AU4" s="4" t="s">
+      <c r="AT4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AV4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="4">
-        <v>2</v>
-      </c>
-      <c r="AX4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="4" t="s">
+      <c r="AV4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AZ4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="BB4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE4" s="4">
+      <c r="AZ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="9">
         <v>5513600</v>
       </c>
-      <c r="BF4" s="4">
+      <c r="BF4" s="9">
         <v>551360</v>
       </c>
-      <c r="BG4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="4">
+      <c r="BG4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="9">
         <v>2025000</v>
       </c>
-      <c r="BJ4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BO4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BP4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BQ4" s="4">
+      <c r="BJ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BM4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BN4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BO4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="9">
         <v>144840</v>
       </c>
-      <c r="BR4" s="4">
+      <c r="BR4" s="9">
         <v>123522</v>
       </c>
-      <c r="BS4" s="4">
+      <c r="BS4" s="9">
         <v>323598</v>
       </c>
-      <c r="BT4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BU4" s="4">
+      <c r="BT4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BU4" s="9">
         <v>13233</v>
       </c>
-      <c r="BV4" s="4">
+      <c r="BV4" s="9">
         <v>39698</v>
       </c>
-      <c r="BW4" s="4">
-        <v>0</v>
-      </c>
-      <c r="BX4" s="4">
+      <c r="BW4" s="9">
+        <v>0</v>
+      </c>
+      <c r="BX4" s="9">
         <v>97</v>
       </c>
-      <c r="BY4" s="4">
+      <c r="BY4" s="9">
         <v>8734948</v>
       </c>
-      <c r="BZ4" s="4">
+      <c r="BZ4" s="9">
         <v>80900</v>
       </c>
-      <c r="CA4" s="4">
+      <c r="CA4" s="9">
         <v>323598</v>
       </c>
-      <c r="CB4" s="4">
+      <c r="CB4" s="9">
         <v>485197</v>
       </c>
-      <c r="CC4" s="4">
+      <c r="CC4" s="9">
         <v>123522</v>
       </c>
-      <c r="CD4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CE4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CF4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CG4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CH4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CI4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CJ4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CK4" s="4">
+      <c r="CD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CF4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CG4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CH4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CI4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CJ4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CK4" s="9">
         <v>13233</v>
       </c>
-      <c r="CL4" s="4">
+      <c r="CL4" s="9">
         <v>39698</v>
       </c>
-      <c r="CM4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO4" s="4">
+      <c r="CM4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CN4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CO4" s="9">
         <v>1066148</v>
       </c>
-      <c r="CP4" s="4">
+      <c r="CP4" s="9">
         <v>7668800</v>
       </c>
-      <c r="CQ4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="CR4" s="4">
-        <v>1</v>
-      </c>
-      <c r="CS4" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT4" s="4">
-        <v>2</v>
-      </c>
-      <c r="CU4" s="4" t="s">
+      <c r="CQ4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="CR4" s="9">
+        <v>1</v>
+      </c>
+      <c r="CS4" s="9">
+        <v>0</v>
+      </c>
+      <c r="CT4" s="9">
+        <v>2</v>
+      </c>
+      <c r="CU4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="CV4" s="4" t="s">
+      <c r="CV4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="CW4" s="4" t="s">
+      <c r="CW4" s="9" t="s">
         <v>184</v>
       </c>
     </row>
@@ -8762,6 +8886,83 @@
       <c r="BY28" s="7">
         <f>BY16*4%</f>
         <v>202264.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:101" x14ac:dyDescent="0.2">
+      <c r="CG30" s="1">
+        <v>199500</v>
+      </c>
+      <c r="CH30" s="1">
+        <v>5</v>
+      </c>
+      <c r="CI30" s="1">
+        <f>CG30*CH30</f>
+        <v>997500</v>
+      </c>
+      <c r="CK30" s="1">
+        <f>45000/10</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:101" x14ac:dyDescent="0.2">
+      <c r="CG31" s="1">
+        <f>78000+CK30</f>
+        <v>82500</v>
+      </c>
+      <c r="CH31" s="1">
+        <v>5</v>
+      </c>
+      <c r="CI31" s="1">
+        <f>CG31*CH31</f>
+        <v>412500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:101" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP32" t="s">
+        <v>365</v>
+      </c>
+      <c r="BY32" s="10">
+        <v>80900</v>
+      </c>
+      <c r="CI32" s="1">
+        <f>CI31+CI30</f>
+        <v>1410000</v>
+      </c>
+    </row>
+    <row r="33" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP33" t="s">
+        <v>366</v>
+      </c>
+      <c r="BY33" s="10">
+        <v>288086</v>
+      </c>
+    </row>
+    <row r="34" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP34" t="s">
+        <v>367</v>
+      </c>
+      <c r="BY34" s="10">
+        <v>197111</v>
+      </c>
+    </row>
+    <row r="35" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP35" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="36" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP36" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="37" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP37" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38" spans="68:77" ht="15" x14ac:dyDescent="0.25">
+      <c r="BP38" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
